--- a/issuesNRISS/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/issuesNRISS/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:17:10+00:00</t>
+    <t>2026-06-18T14:12:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -693,11 +693,11 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-administration-document)
+    <t xml:space="preserve">Reference(Observation|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-administration-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-procedure-document)
 </t>
   </si>
   <si>
-    <t>Observation de score ou administration de médicament associée à l'acte (ex. : produit administré lors d'un acte d'imagerie).</t>
+    <t>Événement associé : score (Cormack ou ASA), administration de médicament ou procédure associée à l’acte (ex. produit administré lors d’un acte d’imagerie).</t>
   </si>
   <si>
     <t>A larger event of which this particular procedure is a component or step.</t>
